--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Kannambakkam_13.493501_80.030121.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Kannambakkam_13.493501_80.030121.xlsx
@@ -974,11 +974,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -986,11 +981,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8A, 8B, 8C, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -998,11 +988,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1010,11 +995,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>-, 1, 10, 11, 12, 13, 14, 15, 2, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1022,11 +1002,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6A, 6B, 6C, 7A, 7B, 7C, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1034,11 +1009,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1046,11 +1016,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1058,11 +1023,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1070,11 +1030,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1082,11 +1037,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10A, 10B, 10C, 10D, 10E, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1094,11 +1044,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 2C, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1106,11 +1051,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18A, 18B, 18C, 18D, 19A, 19B, 1A, 1A1, 1B, 20A, 20B, 20C, 21A, 21B, 22, 23A, 23B, 23C1, 23C2, 23D, 23E, 23F, 23G, 23H, 23I1, 23I2, 23I3, 2A, 2B, 3A1, 3A2, 3B, 4A, 4B, 5, 6A, 6B, 6C, 7, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1118,11 +1058,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1130,11 +1065,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1142,11 +1072,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>-, 8</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1154,11 +1079,6 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1166,11 +1086,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2, 3A, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1178,11 +1093,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1190,11 +1100,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1202,11 +1107,6 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1214,11 +1114,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 18, 19, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1226,11 +1121,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 10C, 10D, 11, 12, 13, 14, 15, 16A, 16B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1238,11 +1128,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1250,11 +1135,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1262,11 +1142,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1274,11 +1149,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>10, 11, 1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1286,11 +1156,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1298,11 +1163,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2A, 2B, 3A, 3B, 3C, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1310,11 +1170,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1322,11 +1177,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1334,11 +1184,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1346,11 +1191,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1358,11 +1198,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1370,11 +1205,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1382,11 +1212,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 6D, 7A, 7B, 8</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1394,11 +1219,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1A1A, 1A1B, 1A2, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1406,11 +1226,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 18A, 18B, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1418,11 +1233,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1430,11 +1240,6 @@
           <t>52</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1442,11 +1247,6 @@
           <t>53</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1454,11 +1254,6 @@
           <t>54</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1466,11 +1261,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14A, 14B, 15, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1478,11 +1268,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2A, 2B, 3, 4A, 4B, 5, 6, 7A, 7B, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1490,11 +1275,6 @@
           <t>57</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1502,11 +1282,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1514,11 +1289,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1526,11 +1296,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1538,11 +1303,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1550,11 +1310,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1562,11 +1317,6 @@
           <t>62</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1574,11 +1324,6 @@
           <t>63</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2A, 2B, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1586,11 +1331,6 @@
           <t>64</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B1, 7B2, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1598,11 +1338,6 @@
           <t>65</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1610,11 +1345,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1622,11 +1352,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1634,11 +1359,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1646,11 +1366,6 @@
           <t>69</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 18, 19, 2, 20A, 20B, 21, 22, 23, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1658,11 +1373,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1670,11 +1380,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1682,11 +1387,6 @@
           <t>71</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1694,11 +1394,6 @@
           <t>72</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 10C, 10D, 10E, 10F, 10G, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1706,11 +1401,6 @@
           <t>73</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1718,11 +1408,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12A, 12B, 13A, 13B, 13C, 14, 15A, 15B, 16, 17, 18, 19, 20A, 20B, 20C, 20D, 21, 22, 23, 24, 25, 26, 27, 28B, 28C, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1730,11 +1415,6 @@
           <t>75</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18A, 18B, 18C, 19, 20, 21, 22, 23, 24, 25A, 25B, 25C, 25D, 25E, 26A, 26B, 26C, 27, 28, 29, 2A, 2B, 2C, 3, 30, 31, 32, 33A, 33B, 34, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1742,11 +1422,6 @@
           <t>76</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28A, 28B, 29, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1754,11 +1429,6 @@
           <t>77</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1766,11 +1436,6 @@
           <t>78</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1778,11 +1443,6 @@
           <t>79</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2A1, 2A2, 2A3, 2B, 2C, 3A1, 3A2, 3A3, 3B, 4, 5A, 5B, 6, 7, 8, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1790,11 +1450,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1802,11 +1457,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 10C, 11A, 11B, 11C, 12, 13A, 13B, 13C, 14A, 14B, 2A1, 2A2, 2A3, 2A4, 2B, 2C, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1814,11 +1464,6 @@
           <t>81</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1826,11 +1471,6 @@
           <t>82</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1838,11 +1478,6 @@
           <t>83</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30A, 30B, 31, 3A, 3B, 3C, 3D, 3E, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 4I, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F, 6G, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1850,11 +1485,6 @@
           <t>84</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 12F, 12G, 12H, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23A1, 23A2, 23A3, 23A4, 23A5, 23B, 24A, 24B, 25, 26, 27A, 27B, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B1A, 7B1B, 7B1C, 7B2, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1862,11 +1492,6 @@
           <t>85</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1A1, 1A2, 1B, 1C, 20A, 20B1, 20B2, 2A, 2B, 2C, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1874,11 +1499,6 @@
           <t>86</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24A, 24B, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1886,11 +1506,6 @@
           <t>87</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 22, 23, 2A, 2B, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1898,11 +1513,6 @@
           <t>88</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1910,11 +1520,6 @@
           <t>89</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>10, 1A1, 1A2, 1A3, 1B, 1C, 1D, 2A1, 2A2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1922,11 +1527,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1934,11 +1534,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1946,11 +1541,6 @@
           <t>91</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1, 2, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 4C, 5A, 5B, 6A1, 6A2, 6B, 7A, 7B, 7C, 7D, 8A, 8B, 8C, 8D</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1958,11 +1548,6 @@
           <t>92</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 2D, 3A, 3B, 4A1, 4A2, 4B, 4C1, 4C2</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1970,11 +1555,6 @@
           <t>93</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 21C, 22, 23A, 23B, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 2C1A, 2C1B, 2C2, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1982,11 +1562,6 @@
           <t>94</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A1, 16A2, 16B, 16C, 17A, 17B, 17C, 17D, 18, 19, 2, 20A, 20B, 20C, 20D, 20E, 20F, 20G, 20H, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1994,11 +1569,6 @@
           <t>95</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2006,11 +1576,6 @@
           <t>96</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2018,11 +1583,6 @@
           <t>97</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B1, 2B2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2030,21 +1590,11 @@
           <t>98</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>1, 10, 11A, 11B, 11C, 11D, 12, 13, 14, 15, 16A, 16B, 17, 18A, 18B, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Kannambakkam_13.493501_80.030121.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Kannambakkam_13.493501_80.030121.xlsx
@@ -998,6 +998,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1005,6 +1010,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-, 1, 10, 11, 12, 13, 14, 15, 2, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1012,6 +1022,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6A, 6B, 6C, 7A, 7B, 7C, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1019,6 +1034,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1026,6 +1046,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1033,6 +1058,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1040,6 +1070,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1047,6 +1082,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 10E, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1054,6 +1094,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 2C, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1061,6 +1106,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18A, 18B, 18C, 18D, 19A, 19B, 1A, 1A1, 1B, 20A, 20B, 20C, 21A, 21B, 22, 23A, 23B, 23C1, 23C2, 23D, 23E, 23F, 23G, 23H, 23I1, 23I2, 23I3, 2A, 2B, 3A1, 3A2, 3B, 4A, 4B, 5, 6A, 6B, 6C, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1068,6 +1118,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1075,6 +1130,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1082,6 +1142,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-, 8</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1089,6 +1154,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1096,6 +1166,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3A, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1103,6 +1178,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1110,6 +1190,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1117,6 +1202,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1124,6 +1214,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 18, 19, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1131,6 +1226,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 11, 12, 13, 14, 15, 16A, 16B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1138,6 +1238,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1145,6 +1250,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1152,6 +1262,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1159,6 +1274,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1166,6 +1286,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1173,6 +1298,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2A, 2B, 3A, 3B, 3C, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1180,6 +1310,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1187,6 +1322,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1194,6 +1334,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1201,6 +1346,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1208,6 +1358,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1215,6 +1370,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1222,6 +1382,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 6D, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1229,6 +1394,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1236,6 +1406,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 18A, 18B, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1243,6 +1418,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1250,6 +1430,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1257,6 +1442,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1264,6 +1454,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1271,6 +1466,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A, 14B, 15, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1278,6 +1478,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2A, 2B, 3, 4A, 4B, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1285,6 +1490,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1292,6 +1502,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1299,6 +1514,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1306,6 +1526,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1313,6 +1538,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1320,6 +1550,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1327,6 +1562,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1334,6 +1574,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2A, 2B, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1341,6 +1586,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B1, 7B2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1348,6 +1598,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1355,6 +1610,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1362,6 +1622,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1369,6 +1634,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1376,6 +1646,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 18, 19, 2, 20A, 20B, 21, 22, 23, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1383,6 +1658,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1390,6 +1670,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1397,6 +1682,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1404,6 +1694,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 10E, 10F, 10G, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1411,6 +1706,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1418,6 +1718,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 13A, 13B, 13C, 14, 15A, 15B, 16, 17, 18, 19, 20A, 20B, 20C, 20D, 21, 22, 23, 24, 25, 26, 27, 28B, 28C, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1425,6 +1730,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18A, 18B, 18C, 19, 20, 21, 22, 23, 24, 25A, 25B, 25C, 25D, 25E, 26A, 26B, 26C, 27, 28, 29, 2A, 2B, 2C, 3, 30, 31, 32, 33A, 33B, 34, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1432,6 +1742,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28A, 28B, 29, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1439,6 +1754,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1446,6 +1766,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1453,6 +1778,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2A1, 2A2, 2A3, 2B, 2C, 3A1, 3A2, 3A3, 3B, 4, 5A, 5B, 6, 7, 8, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1460,6 +1790,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1467,6 +1802,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11A, 11B, 11C, 12, 13A, 13B, 13C, 14A, 14B, 2A1, 2A2, 2A3, 2A4, 2B, 2C, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1474,6 +1814,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1481,6 +1826,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1488,6 +1838,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30A, 30B, 31, 3A, 3B, 3C, 3D, 3E, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 4I, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F, 6G, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1495,6 +1850,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 12F, 12G, 12H, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23A1, 23A2, 23A3, 23A4, 23A5, 23B, 24A, 24B, 25, 26, 27A, 27B, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B1A, 7B1B, 7B1C, 7B2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1502,6 +1862,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1A1, 1A2, 1B, 1C, 20A, 20B1, 20B2, 2A, 2B, 2C, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1509,6 +1874,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24A, 24B, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1516,6 +1886,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 22, 23, 2A, 2B, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1523,6 +1898,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1530,6 +1910,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10, 1A1, 1A2, 1A3, 1B, 1C, 1D, 2A1, 2A2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1537,6 +1922,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1544,6 +1934,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1551,6 +1946,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 2, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 4C, 5A, 5B, 6A1, 6A2, 6B, 7A, 7B, 7C, 7D, 8A, 8B, 8C, 8D</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1558,6 +1958,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D, 3A, 3B, 4A1, 4A2, 4B, 4C1, 4C2</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1565,6 +1970,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 21C, 22, 23A, 23B, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 2C1A, 2C1B, 2C2, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1572,6 +1982,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A1, 16A2, 16B, 16C, 17A, 17B, 17C, 17D, 18, 19, 2, 20A, 20B, 20C, 20D, 20E, 20F, 20G, 20H, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1579,6 +1994,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1586,6 +2006,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1593,6 +2018,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1600,11 +2030,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 12, 13, 14, 15, 16A, 16B, 17, 18A, 18B, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Kannambakkam_13.493501_80.030121.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Kannambakkam_13.493501_80.030121.xlsx
@@ -974,6 +974,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -981,6 +986,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17A, 17B, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8A, 8B, 8C, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -988,6 +998,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -995,6 +1010,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-, 1, 10, 11, 12, 13, 14, 15, 2, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1002,6 +1022,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2, 3, 4, 5, 6A, 6B, 6C, 7A, 7B, 7C, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1009,6 +1034,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1016,6 +1046,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1023,6 +1058,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1030,6 +1070,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1037,6 +1082,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10A, 10B, 10C, 10D, 10E, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1044,6 +1094,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 2C, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1051,6 +1106,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18A, 18B, 18C, 18D, 19A, 19B, 1A, 1A1, 1B, 20A, 20B, 20C, 21A, 21B, 22, 23A, 23B, 23C1, 23C2, 23D, 23E, 23F, 23G, 23H, 23I1, 23I2, 23I3, 2A, 2B, 3A1, 3A2, 3B, 4A, 4B, 5, 6A, 6B, 6C, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1058,6 +1118,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1065,6 +1130,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1072,6 +1142,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-, 8</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1079,6 +1154,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1086,6 +1166,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3A, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1093,6 +1178,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1100,6 +1190,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 14C, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1107,6 +1202,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1114,6 +1214,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 18, 19, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 5C, 5D, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1121,6 +1226,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 11, 12, 13, 14, 15, 16A, 16B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1128,6 +1238,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1135,6 +1250,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 16D, 17, 18, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1142,6 +1262,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1149,6 +1274,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1156,6 +1286,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1163,6 +1298,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2A, 2B, 3A, 3B, 3C, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1170,6 +1310,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1177,6 +1322,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1184,6 +1334,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1191,6 +1346,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1198,6 +1358,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1205,6 +1370,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1212,6 +1382,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 6C, 6D, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1219,6 +1394,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1226,6 +1406,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 16C, 17, 18A, 18B, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1233,6 +1418,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1240,6 +1430,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 2, 3, 4, 5A, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1247,6 +1442,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1254,6 +1454,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1261,6 +1466,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14A, 14B, 15, 1A, 1B, 1C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1268,6 +1478,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 2A, 2B, 3, 4A, 4B, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1275,6 +1490,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1282,6 +1502,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1289,6 +1514,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1296,6 +1526,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1303,6 +1538,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1310,6 +1550,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1317,6 +1562,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 2A, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1324,6 +1574,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 14, 15, 16, 17, 18, 19, 2A, 2B, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1331,6 +1586,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B1, 7B2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1338,6 +1598,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E, 6</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1345,6 +1610,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1352,6 +1622,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1359,6 +1634,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1366,6 +1646,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14, 15, 16, 17A, 17B, 18, 19, 2, 20A, 20B, 21, 22, 23, 3, 4, 5, 6, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1373,6 +1658,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1380,6 +1670,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1387,6 +1682,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1394,6 +1694,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 10D, 10E, 10F, 10G, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1401,6 +1706,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1408,6 +1718,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 13A, 13B, 13C, 14, 15A, 15B, 16, 17, 18, 19, 20A, 20B, 20C, 20D, 21, 22, 23, 24, 25, 26, 27, 28B, 28C, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1415,6 +1730,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18A, 18B, 18C, 19, 20, 21, 22, 23, 24, 25A, 25B, 25C, 25D, 25E, 26A, 26B, 26C, 27, 28, 29, 2A, 2B, 2C, 3, 30, 31, 32, 33A, 33B, 34, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1422,6 +1742,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28A, 28B, 29, 2A, 2B, 3A, 3B, 3C, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1429,6 +1754,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1436,6 +1766,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1443,6 +1778,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 2A1, 2A2, 2A3, 2B, 2C, 3A1, 3A2, 3A3, 3B, 4, 5A, 5B, 6, 7, 8, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1450,6 +1790,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1457,6 +1802,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11A, 11B, 11C, 12, 13A, 13B, 13C, 14A, 14B, 2A1, 2A2, 2A3, 2A4, 2B, 2C, 3, 4, 5, 6, 7, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1464,6 +1814,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1471,6 +1826,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1478,6 +1838,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30A, 30B, 31, 3A, 3B, 3C, 3D, 3E, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 4I, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F, 6G, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1485,6 +1850,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 12F, 12G, 12H, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21A, 21B, 22, 23A1, 23A2, 23A3, 23A4, 23A5, 23B, 24A, 24B, 25, 26, 27A, 27B, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B1A, 7B1B, 7B1C, 7B2, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1492,6 +1862,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1A1, 1A2, 1B, 1C, 20A, 20B1, 20B2, 2A, 2B, 2C, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1499,6 +1874,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24A, 24B, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1506,6 +1886,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 22, 23, 2A, 2B, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1513,6 +1898,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 1A, 1B, 2A, 2B, 2C, 2D, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1520,6 +1910,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10, 1A1, 1A2, 1A3, 1B, 1C, 1D, 2A1, 2A2, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1527,6 +1922,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1534,6 +1934,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1541,6 +1946,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 2, 2B, 2C, 3A, 3B, 3C, 3D, 4A, 4B, 4C, 5A, 5B, 6A1, 6A2, 6B, 7A, 7B, 7C, 7D, 8A, 8B, 8C, 8D</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1548,6 +1958,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D, 3A, 3B, 4A1, 4A2, 4B, 4C1, 4C2</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1555,6 +1970,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21A, 21B, 21C, 22, 23A, 23B, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 2C1A, 2C1B, 2C2, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1562,6 +1982,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A1, 16A2, 16B, 16C, 17A, 17B, 17C, 17D, 18, 19, 2, 20A, 20B, 20C, 20D, 20E, 20F, 20G, 20H, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1569,6 +1994,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1576,6 +2006,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1583,6 +2018,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1590,11 +2030,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C, 11D, 12, 13, 14, 15, 16A, 16B, 17, 18A, 18B, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7A, 7B, 7C, 7D, 8, 9</t>
         </is>
       </c>
     </row>
